--- a/databases/tabela_resumo_clusters_ans_final_kmeans3.xlsx
+++ b/databases/tabela_resumo_clusters_ans_final_kmeans3.xlsx
@@ -414,11 +414,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1: lowest unsafe abortion rates</t>
+          <t>1: lowest induced abortion rates</t>
         </is>
       </c>
       <c r="C2">
-        <v>3857</v>
+        <v>3882</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -433,10 +433,10 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="I2">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J2">
         <v>2.9</v>
@@ -450,11 +450,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2: intermediary unsafe abortion rates</t>
+          <t>2: intermediary induced abortion rates</t>
         </is>
       </c>
       <c r="C3">
-        <v>1335</v>
+        <v>1312</v>
       </c>
       <c r="D3">
         <v>3</v>
@@ -463,13 +463,13 @@
         <v>3.9</v>
       </c>
       <c r="F3">
-        <v>5.47</v>
+        <v>5.46</v>
       </c>
       <c r="G3">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="H3">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="I3">
         <v>6.9</v>
@@ -486,29 +486,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3: highest unsafe abortion rates</t>
+          <t>3: highest induced abortion rates</t>
         </is>
       </c>
       <c r="C4">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="D4">
         <v>9.5</v>
       </c>
       <c r="E4">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="F4">
-        <v>13.4</v>
+        <v>13.45</v>
       </c>
       <c r="G4">
         <v>12.2</v>
       </c>
       <c r="H4">
-        <v>4.29</v>
+        <v>4.41</v>
       </c>
       <c r="I4">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="J4">
         <v>45.4</v>
